--- a/Documentos/Documento 0/Grupo 19 - Evaluacion Costo-Beneficio.xlsx
+++ b/Documentos/Documento 0/Grupo 19 - Evaluacion Costo-Beneficio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\osori\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\osori\Desktop\Otros\UNAB\Igenieria de Software 1\Ingenieria_de_software-Grupo19\Documentos\Documento 0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18848885-57EC-4931-B697-7BC97A242ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1154B6-A30F-465A-8737-ED9A9F25E83B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13740" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RRHH" sheetId="1" r:id="rId1"/>
@@ -780,7 +780,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.85546875" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" customWidth="1"/>
     <col min="4" max="4" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1451,147 +1451,147 @@
         <v>-1000000</v>
       </c>
       <c r="C4" s="21">
-        <f>C2-C3</f>
+        <f t="shared" ref="C4:N4" si="0">C2-C3</f>
         <v>-8500000</v>
       </c>
       <c r="D4" s="21">
-        <f>D2-D3</f>
+        <f t="shared" si="0"/>
         <v>-8500000</v>
       </c>
       <c r="E4" s="21">
-        <f>E2-E3</f>
+        <f t="shared" si="0"/>
         <v>-8500000</v>
       </c>
       <c r="F4" s="21">
-        <f>F2-F3</f>
+        <f t="shared" si="0"/>
         <v>-8500000</v>
       </c>
       <c r="G4" s="21">
-        <f>G2-G3</f>
+        <f t="shared" si="0"/>
         <v>-8500000</v>
       </c>
       <c r="H4" s="21">
-        <f>H2-H3</f>
+        <f t="shared" si="0"/>
         <v>-8500000</v>
       </c>
       <c r="I4" s="21">
-        <f>I2-I3</f>
+        <f t="shared" si="0"/>
         <v>-8500000</v>
       </c>
       <c r="J4" s="21">
-        <f>J2-J3</f>
+        <f t="shared" si="0"/>
         <v>-8500000</v>
       </c>
       <c r="K4" s="21">
-        <f>K2-K3</f>
+        <f t="shared" si="0"/>
         <v>-8500000</v>
       </c>
       <c r="L4" s="21">
-        <f>L2-L3</f>
+        <f t="shared" si="0"/>
         <v>-8500000</v>
       </c>
       <c r="M4" s="21">
-        <f>M2-M3</f>
+        <f t="shared" si="0"/>
         <v>-8500000</v>
       </c>
       <c r="N4" s="21">
-        <f>N2-N3</f>
+        <f t="shared" si="0"/>
         <v>-8500000</v>
       </c>
       <c r="O4" s="21">
-        <f t="shared" ref="O4:Z4" si="0">O2-O3</f>
+        <f t="shared" ref="O4:Z4" si="1">O2-O3</f>
         <v>3990000</v>
       </c>
       <c r="P4" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3990000</v>
       </c>
       <c r="Q4" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3990000</v>
       </c>
       <c r="R4" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3990000</v>
       </c>
       <c r="S4" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3990000</v>
       </c>
       <c r="T4" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3990000</v>
       </c>
       <c r="U4" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3990000</v>
       </c>
       <c r="V4" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3990000</v>
       </c>
       <c r="W4" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3990000</v>
       </c>
       <c r="X4" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3990000</v>
       </c>
       <c r="Y4" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3990000</v>
       </c>
       <c r="Z4" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3990000</v>
       </c>
       <c r="AA4" s="21">
-        <f t="shared" ref="AA4" si="1">AA2-AA3</f>
+        <f t="shared" ref="AA4" si="2">AA2-AA3</f>
         <v>3990000</v>
       </c>
       <c r="AB4" s="21">
-        <f t="shared" ref="AB4" si="2">AB2-AB3</f>
+        <f t="shared" ref="AB4" si="3">AB2-AB3</f>
         <v>3990000</v>
       </c>
       <c r="AC4" s="21">
-        <f t="shared" ref="AC4" si="3">AC2-AC3</f>
+        <f t="shared" ref="AC4" si="4">AC2-AC3</f>
         <v>3990000</v>
       </c>
       <c r="AD4" s="21">
-        <f t="shared" ref="AD4" si="4">AD2-AD3</f>
+        <f t="shared" ref="AD4" si="5">AD2-AD3</f>
         <v>3990000</v>
       </c>
       <c r="AE4" s="21">
-        <f t="shared" ref="AE4" si="5">AE2-AE3</f>
+        <f t="shared" ref="AE4" si="6">AE2-AE3</f>
         <v>3990000</v>
       </c>
       <c r="AF4" s="21">
-        <f t="shared" ref="AF4" si="6">AF2-AF3</f>
+        <f t="shared" ref="AF4" si="7">AF2-AF3</f>
         <v>3990000</v>
       </c>
       <c r="AG4" s="21">
-        <f t="shared" ref="AG4" si="7">AG2-AG3</f>
+        <f t="shared" ref="AG4" si="8">AG2-AG3</f>
         <v>3990000</v>
       </c>
       <c r="AH4" s="21">
-        <f t="shared" ref="AH4" si="8">AH2-AH3</f>
+        <f t="shared" ref="AH4" si="9">AH2-AH3</f>
         <v>3990000</v>
       </c>
       <c r="AI4" s="21">
-        <f t="shared" ref="AI4" si="9">AI2-AI3</f>
+        <f t="shared" ref="AI4" si="10">AI2-AI3</f>
         <v>3990000</v>
       </c>
       <c r="AJ4" s="21">
-        <f t="shared" ref="AJ4" si="10">AJ2-AJ3</f>
+        <f t="shared" ref="AJ4" si="11">AJ2-AJ3</f>
         <v>3990000</v>
       </c>
       <c r="AK4" s="21">
-        <f t="shared" ref="AK4" si="11">AK2-AK3</f>
+        <f t="shared" ref="AK4" si="12">AK2-AK3</f>
         <v>3990000</v>
       </c>
       <c r="AL4" s="21">
-        <f t="shared" ref="AL4" si="12">AL2-AL3</f>
+        <f t="shared" ref="AL4" si="13">AL2-AL3</f>
         <v>3990000</v>
       </c>
     </row>
